--- a/modules/tabs/templates/Crosstab_Config.xlsx
+++ b/modules/tabs/templates/Crosstab_Config.xlsx
@@ -1,30 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Documents/Turas/modules/tabs/templates/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B2563B-0128-F846-A77C-99AA25369009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="21980" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="21980" windowHeight="19200" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Settings" sheetId="1" r:id="rId1"/>
-    <sheet name="Selection" sheetId="2" r:id="rId2"/>
-    <sheet name="Base Filters Reference" sheetId="3" r:id="rId3"/>
-    <sheet name="Comments" sheetId="4" r:id="rId4"/>
-    <sheet name="AddedSlides" sheetId="5" r:id="rId5"/>
+    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Base Filters Reference" sheetId="3" state="visible" r:id="rId2"/>
+    <sheet name="Comments" sheetId="4" state="visible" r:id="rId3"/>
+    <sheet name="AddedSlides" sheetId="5" state="visible" r:id="rId4"/>
+    <sheet name="Selection" sheetId="6" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="358">
   <si>
     <t>TURAS Crosstab Configuration</t>
   </si>
@@ -134,7 +127,7 @@
     <t>weight_variable</t>
   </si>
   <si>
-    <t/>
+    <t>NA</t>
   </si>
   <si>
     <t>Column name in your data that contains weights. Required if apply_weighting = TRUE.</t>
@@ -992,13 +985,125 @@
     <t>- Focus on improving customer service touchpoints
 - Invest in digital channel experience
 - Monitor competitor NPS quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question Selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define which questions appear as stubs (rows) and banners (columns). Blue rows are examples - overwrite with your data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestionCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Include</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UseBanner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BannerBoxCategory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BannerLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DisplayOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CreateIndex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseFilter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CategoryOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestionText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Question code from Survey_Structure. Must match exactly (case-sensitive). For Multi_Mention, use root code (e.g. Q01 not Q01_1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Include this question as a stub (row) in crosstab output.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Use this question's response options as banner (column) breakout groups.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Use BoxCategory groupings instead of individual options for banner columns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Header label for this banner group (e.g. 'Gender', 'Age Group'). Required if UseBanner = Y.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Order of banner columns left to right (1 = leftmost, typically Total).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Calculate mean/index score for this question (Rating, Likert, NPS only).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] R expression to filter respondents (e.g. Q1 == "Male" or !is.na(Q20)). Leave blank for no filter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Group this question under a sidebar category heading. Questions sharing the same category name are grouped together with a collapsible header.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Display order for category groups in the sidebar (integer). Lower numbers appear first. Categories without an order go to the end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Reference only. Has no effect on analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total sample (always include as first banner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q_Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demographics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: demographic banner question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q_Satisfaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: stub question with index score</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1007,43 +1112,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF323367"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF546E7A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <i/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF323367"/>
+      <sz val="10"/>
+      <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1054,30 +1138,56 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color rgb="FFD32F2F"/>
+      <color rgb="FF388E3C"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF546E7A"/>
+      <sz val="14"/>
+      <color rgb="FF323367"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF323367"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF388E3C"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFD32F2F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
     </font>
     <font>
       <sz val="10"/>
@@ -1085,8 +1195,25 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1095,7 +1222,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3E0"/>
+        <fgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECEFF1"/>
       </patternFill>
     </fill>
     <fill>
@@ -1105,12 +1237,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE7"/>
+        <fgColor rgb="FFE8EAF6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECEFF1"/>
+        <fgColor rgb="FFFFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1120,17 +1257,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EAF6"/>
+        <fgColor rgb="FFE3F2FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8F9FA"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F2FD"/>
+        <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1155,7 +1292,6 @@
       <bottom style="thin">
         <color rgb="FFB0BEC5"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1170,63 +1306,67 @@
       <bottom style="thin">
         <color rgb="FF323367"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1523,1561 +1663,1561 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="55.6640625" customWidth="1"/>
-    <col min="5" max="5" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="55.6640625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+    <row r="6">
+      <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="C7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+    <row r="8">
+      <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="C8" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+    <row r="9">
+      <c r="A9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+    <row r="10">
+      <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
+    <row r="11">
+      <c r="A11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+    <row r="14">
+      <c r="A14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="C14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+    <row r="15">
+      <c r="A15" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="C15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+    <row r="16">
+      <c r="A16" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+    <row r="17">
+      <c r="A17" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+    <row r="18">
+      <c r="A18" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+    <row r="19">
+      <c r="A19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
+    <row r="20">
+      <c r="A20" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+    <row r="22">
+      <c r="A22" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="C22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+    <row r="23">
+      <c r="A23" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
+    <row r="24">
+      <c r="A24" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+    <row r="25">
+      <c r="A25" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="C25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+    <row r="26">
+      <c r="A26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
+    <row r="27">
+      <c r="A27" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="C27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="18" t="s">
+    <row r="28">
+      <c r="A28" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="C29" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
+    <row r="30">
+      <c r="A30" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="C30" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
+    <row r="31">
+      <c r="A31" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
+    <row r="32">
+      <c r="A32" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="C32" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
+    <row r="33">
+      <c r="A33" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
+    <row r="34">
+      <c r="A34" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="8" t="b">
+      <c r="B35" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="C35" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
+    <row r="36">
+      <c r="A36" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="10" t="s">
+      <c r="C36" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
+    <row r="37">
+      <c r="A37" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="10" t="s">
+      <c r="C37" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="18" t="s">
+    <row r="38">
+      <c r="A38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-    </row>
-    <row r="39" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A39" s="7" t="s">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="10" t="s">
+      <c r="C39" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A40" s="7" t="s">
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="10" t="s">
+      <c r="C40" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A41" s="7" t="s">
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="10" t="s">
+      <c r="C41" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A42" s="7" t="s">
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="10" t="s">
+      <c r="C42" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="12" t="s">
+    <row r="43">
+      <c r="A43" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="12" t="s">
+    <row r="44">
+      <c r="A44" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="18" t="s">
+    <row r="45">
+      <c r="A45" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="7" t="s">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="10" t="s">
+      <c r="C46" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="7" t="s">
+    <row r="47">
+      <c r="A47" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="10" t="s">
+      <c r="C47" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="7" t="s">
+    <row r="48">
+      <c r="A48" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="C48" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="7" t="s">
+    <row r="49">
+      <c r="A49" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="10" t="s">
+      <c r="C49" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="7" t="s">
+    <row r="50">
+      <c r="A50" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="18" t="s">
+    <row r="51">
+      <c r="A51" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="7" t="s">
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="10" t="s">
+      <c r="C52" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="7" t="s">
+    <row r="53">
+      <c r="A53" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="10" t="s">
+      <c r="C53" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="7" t="s">
+    <row r="54">
+      <c r="A54" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="10" t="s">
+      <c r="C54" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="7" t="s">
+    <row r="55">
+      <c r="A55" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" s="10" t="s">
+      <c r="C55" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="7" t="s">
+    <row r="56">
+      <c r="A56" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="10" t="s">
+      <c r="C56" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="18" t="s">
+    <row r="57">
+      <c r="A57" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-    </row>
-    <row r="58" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A58" s="12" t="s">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="18" t="s">
+    <row r="59">
+      <c r="A59" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="7" t="s">
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="10" t="s">
+      <c r="C60" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="18" t="s">
+    <row r="61">
+      <c r="A61" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="10" t="s">
+      <c r="C62" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="12" t="s">
+    <row r="63">
+      <c r="A63" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="10" t="s">
+      <c r="C64" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="7" t="s">
+    <row r="65">
+      <c r="A65" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+    <row r="66">
+      <c r="A66" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="7" t="s">
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C67" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D67" s="10" t="s">
+      <c r="C67" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="7" t="s">
+    <row r="68">
+      <c r="A68" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="8">
+      <c r="B68" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C68" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="10" t="s">
+      <c r="C68" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="7" t="s">
+    <row r="69">
+      <c r="A69" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C69" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="10" t="s">
+      <c r="C69" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="7" t="s">
+    <row r="70">
+      <c r="A70" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="10" t="s">
+      <c r="C70" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="7" t="s">
+    <row r="71">
+      <c r="A71" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="C71" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" s="10" t="s">
+      <c r="C71" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="7" t="s">
+    <row r="72">
+      <c r="A72" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C72" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="10" t="s">
+      <c r="C72" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="7" t="s">
+    <row r="73">
+      <c r="A73" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="C73" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D73" s="10" t="s">
+      <c r="C73" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="7" t="s">
+    <row r="74">
+      <c r="A74" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C74" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="10" t="s">
+      <c r="C74" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="7" t="s">
+    <row r="75">
+      <c r="A75" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="C75" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="10" t="s">
+      <c r="C75" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="7" t="s">
+    <row r="76">
+      <c r="A76" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="10" t="s">
+      <c r="C76" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="18" t="s">
+    <row r="77">
+      <c r="A77" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="7" t="s">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C78" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="10" t="s">
+      <c r="C78" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="7" t="s">
+    <row r="79">
+      <c r="A79" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D79" s="10" t="s">
+      <c r="C79" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="7" t="s">
+    <row r="80">
+      <c r="A80" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C80" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="10" t="s">
+      <c r="C80" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="7" t="s">
+    <row r="81">
+      <c r="A81" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="10" t="s">
+      <c r="C81" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="52" x14ac:dyDescent="0.2">
-      <c r="A82" s="7" t="s">
+    <row r="82" ht="52" customHeight="1">
+      <c r="A82" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C82" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="10" t="s">
+      <c r="C82" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="7" t="s">
+    <row r="83">
+      <c r="A83" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C83" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D83" s="10" t="s">
+      <c r="C83" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="12" t="s">
+    <row r="84">
+      <c r="A84" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="7" t="s">
+    <row r="85">
+      <c r="A85" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="C85" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85" s="10" t="s">
+      <c r="C85" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="12" t="s">
+    <row r="86">
+      <c r="A86" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="D86" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" s="12" t="s">
+    <row r="87">
+      <c r="A87" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" s="12" t="s">
+    <row r="88">
+      <c r="A88" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="D88" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" s="12" t="s">
+    <row r="89">
+      <c r="A89" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="D89" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" s="18" t="s">
+    <row r="90">
+      <c r="A90" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B90" s="18"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="18"/>
-      <c r="E90" s="18"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" s="12" t="s">
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="12" t="s">
+    <row r="92">
+      <c r="A92" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" s="12" t="s">
+    <row r="93">
+      <c r="A93" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" s="12" t="s">
+    <row r="94">
+      <c r="A94" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" s="18" t="s">
+    <row r="95">
+      <c r="A95" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="B95" s="18"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="12" t="s">
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="D96" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E96" s="11" t="s">
+      <c r="E96" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="12" t="s">
+    <row r="97">
+      <c r="A97" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="D97" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E97" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="12" t="s">
+    <row r="98">
+      <c r="A98" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C98" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="D98" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="E98" s="3" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="12" t="s">
+    <row r="99">
+      <c r="A99" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="10" t="s">
+      <c r="D99" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="12" t="s">
+    <row r="100">
+      <c r="A100" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C100" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D100" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E100" s="3" t="s">
         <v>237</v>
       </c>
     </row>
@@ -3165,897 +3305,377 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="35.6640625" customWidth="1"/>
-    <col min="9" max="9" width="40.6640625" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-    </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="F5" s="14">
-        <v>1</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="14">
-        <v>2</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>297</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F57" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>1</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B5:C57" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D57 G5:G57" xr:uid="{00000000-0002-0000-0100-000003000000}">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>297</v>
-      </c>
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4068,411 +3688,172 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="2" width="60.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="70.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="70.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="14" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+    <row r="5">
+      <c r="A5" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="18" t="s">
         <v>319</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="18" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+    <row r="6">
+      <c r="A6" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+    <row r="7">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4488,4 +3869,217 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="16.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="30.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" t="s">
+        <v>346</v>
+      </c>
+      <c r="F5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F6" t="s">
+        <v>353</v>
+      </c>
+      <c r="G6" t="s">
+        <v>347</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6" t="s">
+        <v>354</v>
+      </c>
+      <c r="J6" t="s">
+        <v>349</v>
+      </c>
+      <c r="K6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H7"/>
+      <c r="I7" t="s">
+        <v>357</v>
+      </c>
+      <c r="J7" t="s">
+        <v>353</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/modules/tabs/templates/Crosstab_Config.xlsx
+++ b/modules/tabs/templates/Crosstab_Config.xlsx
@@ -1,23 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Documents/Turas/modules/tabs/templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A322E9BF-98F4-A245-ADC2-680F71CFC5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="21980" windowHeight="19200" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="22960" yWindow="1340" windowWidth="21980" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Base Filters Reference" sheetId="3" state="visible" r:id="rId2"/>
-    <sheet name="Comments" sheetId="4" state="visible" r:id="rId3"/>
-    <sheet name="AddedSlides" sheetId="5" state="visible" r:id="rId4"/>
-    <sheet name="Selection" sheetId="6" state="visible" r:id="rId5"/>
+    <sheet name="Settings" sheetId="1" r:id="rId1"/>
+    <sheet name="Base Filters Reference" sheetId="3" r:id="rId2"/>
+    <sheet name="Comments" sheetId="4" r:id="rId3"/>
+    <sheet name="AddedSlides" sheetId="5" r:id="rId4"/>
+    <sheet name="Selection" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="358">
   <si>
     <t>TURAS Crosstab Configuration</t>
   </si>
@@ -733,88 +740,10 @@
     <t>Any text (supports markdown)</t>
   </si>
   <si>
-    <t>Question Selection</t>
-  </si>
-  <si>
-    <t>Define which questions appear as stubs (rows) and banners (columns). Blue rows are examples - overwrite with your data.</t>
-  </si>
-  <si>
     <t>QuestionCode</t>
   </si>
   <si>
-    <t>Include</t>
-  </si>
-  <si>
-    <t>UseBanner</t>
-  </si>
-  <si>
-    <t>BannerBoxCategory</t>
-  </si>
-  <si>
-    <t>BannerLabel</t>
-  </si>
-  <si>
-    <t>DisplayOrder</t>
-  </si>
-  <si>
-    <t>CreateIndex</t>
-  </si>
-  <si>
-    <t>BaseFilter</t>
-  </si>
-  <si>
-    <t>QuestionText</t>
-  </si>
-  <si>
-    <t>[REQUIRED] Question code from Survey_Structure. Must match exactly (case-sensitive). For Multi_Mention, use root code (e.g. Q01 not Q01_1).</t>
-  </si>
-  <si>
-    <t>[REQUIRED] Include this question as a stub (row) in crosstab output.</t>
-  </si>
-  <si>
-    <t>[REQUIRED] Use this question's response options as banner (column) breakout groups.</t>
-  </si>
-  <si>
-    <t>[Optional] Use BoxCategory groupings instead of individual options for banner columns.</t>
-  </si>
-  <si>
-    <t>[Optional] Header label for this banner group (e.g. 'Gender', 'Age Group'). Required if UseBanner = Y.</t>
-  </si>
-  <si>
-    <t>[Optional] Order of banner columns left to right (1 = leftmost, typically Total).</t>
-  </si>
-  <si>
-    <t>[Optional] Calculate mean/index score for this question (Rating, Likert, NPS only).</t>
-  </si>
-  <si>
-    <t>[Optional] R expression to filter respondents (e.g. Q1 == "Male" or !is.na(Q20)). Leave blank for no filter.</t>
-  </si>
-  <si>
-    <t>[Optional] Reference only - question wording for your convenience. Not used in processing.</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Total sample (always include as first banner)</t>
-  </si>
-  <si>
-    <t>Q_Gender</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Example: demographic banner question</t>
-  </si>
-  <si>
     <t>Q_Satisfaction</t>
-  </si>
-  <si>
-    <t>Example: stub question with index score</t>
   </si>
   <si>
     <t>Base Filter Reference Guide</t>
@@ -987,123 +916,197 @@
 - Monitor competitor NPS quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Question Selection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define which questions appear as stubs (rows) and banners (columns). Blue rows are examples - overwrite with your data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuestionCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UseBanner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BannerBoxCategory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BannerLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DisplayOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CreateIndex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BaseFilter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CategoryOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuestionText</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Question code from Survey_Structure. Must match exactly (case-sensitive). For Multi_Mention, use root code (e.g. Q01 not Q01_1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Include this question as a stub (row) in crosstab output.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Use this question's response options as banner (column) breakout groups.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Use BoxCategory groupings instead of individual options for banner columns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Header label for this banner group (e.g. 'Gender', 'Age Group'). Required if UseBanner = Y.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Order of banner columns left to right (1 = leftmost, typically Total).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Calculate mean/index score for this question (Rating, Likert, NPS only).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] R expression to filter respondents (e.g. Q1 == "Male" or !is.na(Q20)). Leave blank for no filter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Group this question under a sidebar category heading. Questions sharing the same category name are grouped together with a collapsible header.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Display order for category groups in the sidebar (integer). Lower numbers appear first. Categories without an order go to the end.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Reference only. Has no effect on analysis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total sample (always include as first banner)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demographics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example: demographic banner question</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_Satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example: stub question with index score</t>
+    <t>Question Selection</t>
+  </si>
+  <si>
+    <t>Define which questions appear as stubs (rows) and banners (columns). Blue rows are examples - overwrite with your data.</t>
+  </si>
+  <si>
+    <t>QuestionCode</t>
+  </si>
+  <si>
+    <t>Include</t>
+  </si>
+  <si>
+    <t>UseBanner</t>
+  </si>
+  <si>
+    <t>BannerBoxCategory</t>
+  </si>
+  <si>
+    <t>BannerLabel</t>
+  </si>
+  <si>
+    <t>DisplayOrder</t>
+  </si>
+  <si>
+    <t>CreateIndex</t>
+  </si>
+  <si>
+    <t>BaseFilter</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>CategoryOrder</t>
+  </si>
+  <si>
+    <t>QuestionText</t>
+  </si>
+  <si>
+    <t>[REQUIRED] Question code from Survey_Structure. Must match exactly (case-sensitive). For Multi_Mention, use root code (e.g. Q01 not Q01_1).</t>
+  </si>
+  <si>
+    <t>[REQUIRED] Include this question as a stub (row) in crosstab output.</t>
+  </si>
+  <si>
+    <t>[REQUIRED] Use this question's response options as banner (column) breakout groups.</t>
+  </si>
+  <si>
+    <t>[Optional] Use BoxCategory groupings instead of individual options for banner columns.</t>
+  </si>
+  <si>
+    <t>[Optional] Header label for this banner group (e.g. 'Gender', 'Age Group'). Required if UseBanner = Y.</t>
+  </si>
+  <si>
+    <t>[Optional] Order of banner columns left to right (1 = leftmost, typically Total).</t>
+  </si>
+  <si>
+    <t>[Optional] Calculate mean/index score for this question (Rating, Likert, NPS only).</t>
+  </si>
+  <si>
+    <t>[Optional] R expression to filter respondents (e.g. Q1 == "Male" or !is.na(Q20)). Leave blank for no filter.</t>
+  </si>
+  <si>
+    <t>[Optional] Group this question under a sidebar category heading. Questions sharing the same category name are grouped together with a collapsible header.</t>
+  </si>
+  <si>
+    <t>[Optional] Display order for category groups in the sidebar (integer). Lower numbers appear first. Categories without an order go to the end.</t>
+  </si>
+  <si>
+    <t>[Optional] Reference only. Has no effect on analysis.</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Total sample (always include as first banner)</t>
+  </si>
+  <si>
+    <t>Q_Gender</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>Example: demographic banner question</t>
+  </si>
+  <si>
+    <t>Q_Satisfaction</t>
+  </si>
+  <si>
+    <t>Satisfaction</t>
+  </si>
+  <si>
+    <t>Example: stub question with index score</t>
+  </si>
+  <si>
+    <t>chart_series_colour_1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Custom colour for 1st banner series in bar charts (e.g., Total). Leave blank to auto-generate.</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g. #1B365D)</t>
+  </si>
+  <si>
+    <t>chart_series_colour_2</t>
+  </si>
+  <si>
+    <t>Custom colour for 2nd banner series in bar charts.</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g. #3A6EA5)</t>
+  </si>
+  <si>
+    <t>chart_series_colour_3</t>
+  </si>
+  <si>
+    <t>Custom colour for 3rd banner series in bar charts.</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g. #E87722)</t>
+  </si>
+  <si>
+    <t>chart_series_colour_4</t>
+  </si>
+  <si>
+    <t>Custom colour for 4th banner series in bar charts.</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g. #5B9A7D)</t>
+  </si>
+  <si>
+    <t>chart_series_colour_5</t>
+  </si>
+  <si>
+    <t>Custom colour for 5th banner series in bar charts.</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g. #8E4585)</t>
+  </si>
+  <si>
+    <t>chart_series_colour_6</t>
+  </si>
+  <si>
+    <t>Custom colour for 6th banner series in bar charts.</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g. #C14D00)</t>
+  </si>
+  <si>
+    <t>chart_series_colour_7</t>
+  </si>
+  <si>
+    <t>Custom colour for 7th banner series in bar charts.</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g. #4A7C6F)</t>
+  </si>
+  <si>
+    <t>chart_series_colour_8</t>
+  </si>
+  <si>
+    <t>Custom colour for 8th banner series in bar charts. If more series than colours, colours cycle.</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g. #D4918E)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1112,18 +1115,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="9"/>
       <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <i/>
     </font>
     <font>
       <sz val="10"/>
@@ -1144,30 +1147,31 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
       <color rgb="FF323367"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="10"/>
       <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <i/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF323367"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
     </font>
     <font>
       <sz val="9"/>
@@ -1176,18 +1180,18 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FFD32F2F"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
     </font>
     <font>
       <sz val="10"/>
@@ -1196,16 +1200,16 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
-      <b/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <b/>
     </font>
     <font>
       <sz val="9"/>
@@ -1292,6 +1296,7 @@
       <bottom style="thin">
         <color rgb="FFB0BEC5"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1306,6 +1311,7 @@
       <bottom style="thin">
         <color rgb="FF323367"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -1325,16 +1331,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1367,6 +1363,16 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1663,86 +1669,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E108"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="55.6640625" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="55.6640625" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1752,14 +1758,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -1769,14 +1775,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -1786,14 +1792,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -1803,23 +1809,23 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="15" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -1829,11 +1835,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -1846,14 +1852,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -1863,14 +1869,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -1880,14 +1886,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -1897,14 +1903,14 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="12">
         <v>10</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -1914,14 +1920,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="12">
         <v>5</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -1931,14 +1937,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="12">
         <v>3</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -1948,23 +1954,23 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="s">
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -1974,14 +1980,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -1991,14 +1997,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -2008,14 +2014,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -2025,14 +2031,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -2042,11 +2048,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -2059,14 +2065,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -2076,23 +2082,23 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="s">
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -2102,14 +2108,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="12">
         <v>0</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -2119,14 +2125,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="15" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="12">
         <v>1</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -2136,14 +2142,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="12">
         <v>1</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -2153,14 +2159,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="12">
         <v>1</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -2170,23 +2176,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="s">
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="16" t="b">
+      <c r="B35" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -2196,14 +2202,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="15" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -2213,14 +2219,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="2" t="s">
@@ -2230,23 +2236,23 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="15" t="s">
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+    </row>
+    <row r="39" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="2" t="s">
@@ -2256,14 +2262,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="15" t="s">
+    <row r="40" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" s="12">
         <v>0.05</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -2273,14 +2279,14 @@
         <v>97</v>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="15" t="s">
+    <row r="41" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" s="12">
         <v>30</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="2" t="s">
@@ -2290,14 +2296,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -2307,11 +2313,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C43" s="5" t="s">
@@ -2324,11 +2330,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C44" s="5" t="s">
@@ -2341,23 +2347,23 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="s">
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="2" t="s">
@@ -2367,14 +2373,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="2" t="s">
@@ -2384,14 +2390,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="15" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="2" t="s">
@@ -2401,14 +2407,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="15" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -2418,14 +2424,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="2" t="s">
@@ -2435,23 +2441,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="9" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="s">
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="2" t="s">
@@ -2461,14 +2467,14 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="15" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="2" t="s">
@@ -2478,14 +2484,14 @@
         <v>123</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="2" t="s">
@@ -2495,14 +2501,14 @@
         <v>123</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="15" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D55" s="2" t="s">
@@ -2512,14 +2518,14 @@
         <v>123</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="15" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B56" s="16" t="n">
+      <c r="B56" s="12">
         <v>1</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
@@ -2529,20 +2535,20 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="9" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-    </row>
-    <row r="58" ht="26" customHeight="1">
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+    </row>
+    <row r="58" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C58" s="5" t="s">
@@ -2555,23 +2561,23 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="9" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="s">
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="2" t="s">
@@ -2581,23 +2587,23 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="9" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="s">
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="2" t="s">
@@ -2607,11 +2613,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C63" s="5" t="s">
@@ -2624,14 +2630,14 @@
         <v>144</v>
       </c>
     </row>
-    <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="15" t="s">
+    <row r="64" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="2" t="s">
@@ -2641,14 +2647,14 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="15" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="2" t="s">
@@ -2658,23 +2664,23 @@
         <v>152</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="9" t="s">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="s">
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="16" t="n">
+      <c r="B67" s="12">
         <v>10</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="2" t="s">
@@ -2684,14 +2690,14 @@
         <v>156</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="15" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="16" t="n">
+      <c r="B68" s="12">
         <v>10</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -2701,14 +2707,14 @@
         <v>156</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="15" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B69" s="16" t="n">
+      <c r="B69" s="12">
         <v>30</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="2" t="s">
@@ -2718,14 +2724,14 @@
         <v>161</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="15" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B70" s="16" t="n">
+      <c r="B70" s="12">
         <v>0</v>
       </c>
-      <c r="C70" s="17" t="s">
+      <c r="C70" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D70" s="2" t="s">
@@ -2735,14 +2741,14 @@
         <v>161</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="15" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B71" s="16" t="n">
+      <c r="B71" s="12">
         <v>7</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -2752,14 +2758,14 @@
         <v>166</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="15" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B72" s="16" t="n">
+      <c r="B72" s="12">
         <v>5</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="2" t="s">
@@ -2769,14 +2775,14 @@
         <v>166</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="15" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B73" s="16" t="n">
+      <c r="B73" s="12">
         <v>7</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D73" s="2" t="s">
@@ -2786,14 +2792,14 @@
         <v>166</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="15" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="16" t="n">
+      <c r="B74" s="12">
         <v>5</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="C74" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="2" t="s">
@@ -2803,14 +2809,14 @@
         <v>166</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="15" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B75" s="16" t="n">
+      <c r="B75" s="12">
         <v>60</v>
       </c>
-      <c r="C75" s="17" t="s">
+      <c r="C75" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="2" t="s">
@@ -2820,14 +2826,14 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="15" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="B76" s="16" t="n">
+      <c r="B76" s="12">
         <v>40</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="C76" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="2" t="s">
@@ -2837,23 +2843,23 @@
         <v>161</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="9" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="15" t="s">
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="C78" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D78" s="2" t="s">
@@ -2863,14 +2869,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="15" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C79" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="2" t="s">
@@ -2880,14 +2886,14 @@
         <v>183</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="15" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C80" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="2" t="s">
@@ -2897,14 +2903,14 @@
         <v>187</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="15" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B81" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="17" t="s">
+      <c r="C81" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D81" s="2" t="s">
@@ -2914,14 +2920,14 @@
         <v>183</v>
       </c>
     </row>
-    <row r="82" ht="52" customHeight="1">
-      <c r="A82" s="15" t="s">
+    <row r="82" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D82" s="2" t="s">
@@ -2931,315 +2937,451 @@
         <v>193</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="B83" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C83" s="17" t="s">
-        <v>15</v>
+    <row r="83" spans="1:5" ht="26" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>195</v>
+        <v>335</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B84" s="16" t="s">
-        <v>36</v>
+        <v>337</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>334</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>197</v>
+        <v>338</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="B85" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C85" s="17" t="s">
-        <v>15</v>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>201</v>
+        <v>341</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>36</v>
+        <v>343</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>334</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>203</v>
+        <v>344</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B87" s="16" t="s">
-        <v>36</v>
+        <v>346</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>334</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>205</v>
+        <v>347</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B88" s="16" t="s">
-        <v>36</v>
+        <v>349</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>334</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>208</v>
+        <v>350</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B89" s="16" t="s">
-        <v>36</v>
+        <v>352</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>334</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>210</v>
+        <v>353</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B91" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C91" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="26" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="D90" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>15</v>
+      </c>
       <c r="D91" s="2" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B92" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B93" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>4</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B94" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B94" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-    </row>
-    <row r="96">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B96" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B96" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B97" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B97" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B98" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B98" s="18"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="18"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B99" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B99" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B100" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B100" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B103" s="18"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="18"/>
+      <c r="E103" s="18"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E108" s="3" t="s">
         <v>237</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A103:E103"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" sqref="B75:B76 B69:B70 B17:B18" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3277,7 +3419,7 @@
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{00000000-0002-0000-0000-000014000000}">
       <formula1>"xlsx,csv"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B12 B83 B78 B62 B60 B46:B49 B42 B39 B35:B37 B27 B21:B25 B14:B15" xr:uid="{00000000-0002-0000-0000-000015000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B12 B91 B78 B62 B60 B46:B49 B42 B39 B35:B37 B27 B21:B25 B14:B15" xr:uid="{00000000-0002-0000-0000-000015000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B26 B58 B43:B44" xr:uid="{00000000-0002-0000-0000-00001D000000}">
@@ -3305,137 +3447,137 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="B12" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="C12" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B4" s="14" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="B13" s="3" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -3449,233 +3591,233 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="60.6640625" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="60.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="C5" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="C6" s="18" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="C7" s="18" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3688,172 +3830,172 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="70.6640625" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="70.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="C5" s="18" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="C6" s="18" t="n">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3872,214 +4014,194 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="16.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="30.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
+      <c r="D5" t="s">
+        <v>321</v>
+      </c>
+      <c r="E5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F5" t="s">
         <v>323</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="s">
+      <c r="G5" t="s">
+        <v>321</v>
+      </c>
+      <c r="K5" t="s">
         <v>324</v>
       </c>
-      <c r="B3" s="20" t="s">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>325</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="B6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C6" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" t="s">
         <v>326</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="F6" t="s">
         <v>327</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="G6" t="s">
+        <v>321</v>
+      </c>
+      <c r="I6" t="s">
         <v>328</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="J6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K6" t="s">
         <v>329</v>
       </c>
-      <c r="G3" s="20" t="s">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>330</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="B7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G7" t="s">
+        <v>322</v>
+      </c>
+      <c r="I7" t="s">
         <v>331</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="J7" t="s">
+        <v>327</v>
+      </c>
+      <c r="K7" t="s">
         <v>332</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="K3" s="20" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4" ht="50" customHeight="1">
-      <c r="A4" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="K4" s="21" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>346</v>
-      </c>
-      <c r="B5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C5" t="s">
-        <v>348</v>
-      </c>
-      <c r="D5" t="s">
-        <v>347</v>
-      </c>
-      <c r="E5" t="s">
-        <v>346</v>
-      </c>
-      <c r="F5" t="s">
-        <v>349</v>
-      </c>
-      <c r="G5" t="s">
-        <v>347</v>
-      </c>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>351</v>
-      </c>
-      <c r="B6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C6" t="s">
-        <v>348</v>
-      </c>
-      <c r="D6" t="s">
-        <v>347</v>
-      </c>
-      <c r="E6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F6" t="s">
-        <v>353</v>
-      </c>
-      <c r="G6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H6"/>
-      <c r="I6" t="s">
-        <v>354</v>
-      </c>
-      <c r="J6" t="s">
-        <v>349</v>
-      </c>
-      <c r="K6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B7" t="s">
-        <v>348</v>
-      </c>
-      <c r="C7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7" t="s">
-        <v>348</v>
-      </c>
-      <c r="H7"/>
-      <c r="I7" t="s">
-        <v>357</v>
-      </c>
-      <c r="J7" t="s">
-        <v>353</v>
-      </c>
-      <c r="K7" t="s">
-        <v>358</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/modules/tabs/templates/Crosstab_Config.xlsx
+++ b/modules/tabs/templates/Crosstab_Config.xlsx
@@ -1,30 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Documents/Turas/modules/tabs/templates/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E336BF26-B939-6641-928D-49991BBB9902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="24660" windowHeight="13460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="24660" windowHeight="13460" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Settings" sheetId="1" r:id="rId1"/>
-    <sheet name="Selection" sheetId="2" r:id="rId2"/>
-    <sheet name="Base Filters Reference" sheetId="3" r:id="rId3"/>
-    <sheet name="Comments" sheetId="4" r:id="rId4"/>
-    <sheet name="AddedSlides" sheetId="5" r:id="rId5"/>
+    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Selection" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Base Filters Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="AddedSlides" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="365">
   <si>
     <t>TURAS Crosstab Configuration</t>
   </si>
@@ -134,7 +127,7 @@
     <t>weight_variable</t>
   </si>
   <si>
-    <t/>
+    <t>NA</t>
   </si>
   <si>
     <t>Column name in your data that contains weights. Required if apply_weighting = TRUE.</t>
@@ -1115,13 +1108,23 @@
   </si>
   <si>
     <t>set the order of the category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI INSIGHTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enable_ai_insights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALSE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1130,43 +1133,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF323367"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF546E7A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <i/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF323367"/>
+      <sz val="10"/>
+      <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1177,30 +1159,56 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color rgb="FFD32F2F"/>
+      <color rgb="FF388E3C"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF546E7A"/>
+      <sz val="14"/>
+      <color rgb="FF323367"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF323367"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF388E3C"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFD32F2F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
     </font>
     <font>
       <sz val="10"/>
@@ -1208,8 +1216,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1A2744"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1218,7 +1232,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3E0"/>
+        <fgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECEFF1"/>
       </patternFill>
     </fill>
     <fill>
@@ -1228,12 +1247,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE7"/>
+        <fgColor rgb="FFE8EAF6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECEFF1"/>
+        <fgColor rgb="FFFFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1243,17 +1267,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EAF6"/>
+        <fgColor rgb="FFE3F2FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8F9FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F2FD"/>
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1278,7 +1297,6 @@
       <bottom style="thin">
         <color rgb="FFB0BEC5"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1293,64 +1311,65 @@
       <bottom style="thin">
         <color rgb="FF323367"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1646,1775 +1665,1788 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E113"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="55.6640625" customWidth="1"/>
-    <col min="5" max="5" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="55.6640625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+    <row r="6">
+      <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="C7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+    <row r="8">
+      <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="C8" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+    <row r="9">
+      <c r="A9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+    <row r="10">
+      <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
+    <row r="11">
+      <c r="A11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+    <row r="14">
+      <c r="A14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="C14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+    <row r="15">
+      <c r="A15" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="C15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+    <row r="16">
+      <c r="A16" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+    <row r="17">
+      <c r="A17" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+    <row r="18">
+      <c r="A18" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+    <row r="19">
+      <c r="A19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
+    <row r="20">
+      <c r="A20" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+    <row r="22">
+      <c r="A22" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="C22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+    <row r="23">
+      <c r="A23" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
+    <row r="24">
+      <c r="A24" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+    <row r="25">
+      <c r="A25" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="C25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+    <row r="26">
+      <c r="A26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
+    <row r="27">
+      <c r="A27" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="C27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="18" t="s">
+    <row r="28">
+      <c r="A28" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="C29" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
+    <row r="30">
+      <c r="A30" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="C30" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
+    <row r="31">
+      <c r="A31" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
+    <row r="32">
+      <c r="A32" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="C32" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
+    <row r="33">
+      <c r="A33" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
+    <row r="34">
+      <c r="A34" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="C35" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
+    <row r="36">
+      <c r="A36" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="10" t="s">
+      <c r="C36" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
+    <row r="37">
+      <c r="A37" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="10" t="s">
+      <c r="C37" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="18" t="s">
+    <row r="38">
+      <c r="A38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-    </row>
-    <row r="39" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A39" s="7" t="s">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="10" t="s">
+      <c r="C39" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A40" s="7" t="s">
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="10" t="s">
+      <c r="C40" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A41" s="7" t="s">
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="10" t="s">
+      <c r="C41" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A42" s="7" t="s">
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="10" t="s">
+      <c r="C42" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="12" t="s">
+    <row r="43">
+      <c r="A43" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="12" t="s">
+    <row r="44">
+      <c r="A44" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="18" t="s">
+    <row r="45">
+      <c r="A45" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="7" t="s">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="10" t="s">
+      <c r="C46" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="7" t="s">
+    <row r="47">
+      <c r="A47" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="10" t="s">
+      <c r="C47" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="7" t="s">
+    <row r="48">
+      <c r="A48" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="C48" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="7" t="s">
+    <row r="49">
+      <c r="A49" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="10" t="s">
+      <c r="C49" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="7" t="s">
+    <row r="50">
+      <c r="A50" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="18" t="s">
+    <row r="51">
+      <c r="A51" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="7" t="s">
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="10" t="s">
+      <c r="C52" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="7" t="s">
+    <row r="53">
+      <c r="A53" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="10" t="s">
+      <c r="C53" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="7" t="s">
+    <row r="54">
+      <c r="A54" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="10" t="s">
+      <c r="C54" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="7" t="s">
+    <row r="55">
+      <c r="A55" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" s="10" t="s">
+      <c r="C55" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="7" t="s">
+    <row r="56">
+      <c r="A56" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="10" t="s">
+      <c r="C56" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="18" t="s">
+    <row r="57">
+      <c r="A57" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-    </row>
-    <row r="58" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A58" s="12" t="s">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="18" t="s">
+    <row r="59">
+      <c r="A59" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="7" t="s">
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="10" t="s">
+      <c r="C60" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="18" t="s">
+    <row r="61">
+      <c r="A61" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="10" t="s">
+      <c r="C62" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="12" t="s">
+    <row r="63">
+      <c r="A63" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="10" t="s">
+      <c r="C64" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="7" t="s">
+    <row r="65">
+      <c r="A65" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+    <row r="66">
+      <c r="A66" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="7" t="s">
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C67" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D67" s="10" t="s">
+      <c r="C67" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="7" t="s">
+    <row r="68">
+      <c r="A68" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="8">
+      <c r="B68" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C68" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="10" t="s">
+      <c r="C68" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="7" t="s">
+    <row r="69">
+      <c r="A69" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C69" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="10" t="s">
+      <c r="C69" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="7" t="s">
+    <row r="70">
+      <c r="A70" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="10" t="s">
+      <c r="C70" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="7" t="s">
+    <row r="71">
+      <c r="A71" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="C71" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" s="10" t="s">
+      <c r="C71" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="7" t="s">
+    <row r="72">
+      <c r="A72" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C72" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="10" t="s">
+      <c r="C72" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="7" t="s">
+    <row r="73">
+      <c r="A73" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="C73" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D73" s="10" t="s">
+      <c r="C73" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="7" t="s">
+    <row r="74">
+      <c r="A74" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C74" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="10" t="s">
+      <c r="C74" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="7" t="s">
+    <row r="75">
+      <c r="A75" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="C75" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="10" t="s">
+      <c r="C75" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="7" t="s">
+    <row r="76">
+      <c r="A76" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="10" t="s">
+      <c r="C76" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="18" t="s">
+    <row r="77">
+      <c r="A77" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="7" t="s">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C78" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="10" t="s">
+      <c r="C78" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="7" t="s">
+    <row r="79">
+      <c r="A79" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D79" s="10" t="s">
+      <c r="C79" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="7" t="s">
+    <row r="80">
+      <c r="A80" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C80" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="10" t="s">
+      <c r="C80" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="7" t="s">
+    <row r="81">
+      <c r="A81" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="10" t="s">
+      <c r="C81" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="52" x14ac:dyDescent="0.2">
-      <c r="A82" s="7" t="s">
+    <row r="82" ht="52" customHeight="1">
+      <c r="A82" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C82" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="10" t="s">
+      <c r="C82" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="39" x14ac:dyDescent="0.2">
-      <c r="A83" s="12" t="s">
+    <row r="83" ht="39" customHeight="1">
+      <c r="A83" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="12" t="s">
+    <row r="84">
+      <c r="A84" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="12" t="s">
+    <row r="85">
+      <c r="A85" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="12" t="s">
+    <row r="86">
+      <c r="A86" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="D86" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" s="12" t="s">
+    <row r="87">
+      <c r="A87" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" s="12" t="s">
+    <row r="88">
+      <c r="A88" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="D88" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" s="12" t="s">
+    <row r="89">
+      <c r="A89" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="D89" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A90" s="12" t="s">
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="D90" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" s="7" t="s">
+    <row r="91">
+      <c r="A91" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C91" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" s="10" t="s">
+      <c r="C91" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="12" t="s">
+    <row r="92">
+      <c r="A92" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" s="7" t="s">
+    <row r="93">
+      <c r="A93" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="C93" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="10" t="s">
+      <c r="C93" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" s="12" t="s">
+    <row r="94">
+      <c r="A94" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" s="12" t="s">
+    <row r="95">
+      <c r="A95" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="12" t="s">
+    <row r="96">
+      <c r="A96" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="D96" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E96" s="11" t="s">
+      <c r="E96" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="12" t="s">
+    <row r="97">
+      <c r="A97" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="D97" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E97" s="3" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="18" t="s">
+    <row r="98">
+      <c r="A98" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B98" s="18"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="18"/>
-      <c r="E98" s="18"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="12" t="s">
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="10" t="s">
+      <c r="D99" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="3" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="12" t="s">
+    <row r="100">
+      <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C100" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D100" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E100" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="12" t="s">
+    <row r="101">
+      <c r="A101" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="D101" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="E101" s="3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="12" t="s">
+    <row r="102">
+      <c r="A102" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="D102" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E102" s="11" t="s">
+      <c r="E102" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="18" t="s">
+    <row r="103">
+      <c r="A103" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B103" s="18"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="18"/>
-      <c r="E103" s="18"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="12" t="s">
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C104" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="D104" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="E104" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" s="12" t="s">
+    <row r="105">
+      <c r="A105" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="B105" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D105" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E105" s="11" t="s">
+      <c r="E105" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="12" t="s">
+    <row r="106">
+      <c r="A106" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C106" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="D106" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E106" s="11" t="s">
+      <c r="E106" s="3" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" s="12" t="s">
+    <row r="107">
+      <c r="A107" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C107" s="13" t="s">
+      <c r="C107" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="D107" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E107" s="11" t="s">
+      <c r="E107" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="12" t="s">
+    <row r="108">
+      <c r="A108" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="B108" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C108" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E108" s="11" t="s">
+      <c r="E108" s="3" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="39" x14ac:dyDescent="0.2">
-      <c r="A109" s="12" t="s">
+    <row r="109" ht="39" customHeight="1">
+      <c r="A109" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="B109" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="D109" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E109" s="11" t="s">
+      <c r="E109" s="3" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="18" t="s">
+    <row r="110">
+      <c r="A110" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="B110" s="18"/>
-      <c r="C110" s="18"/>
-      <c r="D110" s="18"/>
-      <c r="E110" s="18"/>
-    </row>
-    <row r="111" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A111" s="12" t="s">
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+    </row>
+    <row r="111" ht="26" customHeight="1">
+      <c r="A111" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="B111" s="8" t="s">
+      <c r="B111" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C111" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D111" s="10" t="s">
+      <c r="D111" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E111" s="11" t="s">
+      <c r="E111" s="3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="12" t="s">
+    <row r="112">
+      <c r="A112" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B112" s="8" t="s">
+      <c r="B112" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C112" s="13" t="s">
+      <c r="C112" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="D112" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E112" s="11" t="s">
+      <c r="E112" s="3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="26" x14ac:dyDescent="0.2">
-      <c r="A113" s="12" t="s">
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B113" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C113" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="D113" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E113" s="11" t="s">
+      <c r="E113" s="3" t="s">
         <v>269</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="19" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>364</v>
+      </c>
+      <c r="B116" s="20" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -3505,924 +3537,927 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="11" width="35.6640625" customWidth="1"/>
-    <col min="12" max="12" width="40.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="40.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="14" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+    <row r="5">
+      <c r="A5" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14" t="s">
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+    <row r="6">
+      <c r="A6" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14" t="s">
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+    <row r="7">
+      <c r="A7" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14" t="s">
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="8"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="8"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
+    <row r="8">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="16"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="16"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4447,136 +4482,136 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="14" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+    <row r="5">
+      <c r="A5" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="3" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+    <row r="6">
+      <c r="A6" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+    <row r="7">
+      <c r="A7" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="3" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+    <row r="8">
+      <c r="A8" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="3" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+    <row r="9">
+      <c r="A9" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="3" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+    <row r="10">
+      <c r="A10" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+    <row r="11">
+      <c r="A11" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+    <row r="12">
+      <c r="A12" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+    <row r="13">
+      <c r="A13" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="3" t="s">
         <v>332</v>
       </c>
     </row>
@@ -4591,233 +4626,233 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="2" width="60.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="14" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+    <row r="5">
+      <c r="A5" s="18" t="s">
         <v>340</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+    <row r="6">
+      <c r="A6" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+    <row r="7">
+      <c r="A7" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
+    <row r="8">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4830,172 +4865,172 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="70.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="70.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="14" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+    <row r="5">
+      <c r="A5" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="18" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+    <row r="6">
+      <c r="A6" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+    <row r="7">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
